--- a/workspaces/ArdJan_testset/input/input.xlsx
+++ b/workspaces/ArdJan_testset/input/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oscop\Documents\GeoProb-Pipe\workspaces\ArdJan_testset\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B584EC1D-C2B1-47AA-85ED-118948166F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{810AEE5D-4FC6-4B03-9F1E-6B17DB28F74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E14FA4F5-43AA-4DAE-BCE2-7688F4F5853B}"/>
   </bookViews>
   <sheets>
     <sheet name="Vakken" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Settings" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -669,7 +670,7 @@
     <t>Vak3</t>
   </si>
   <si>
-    <t>198808_433604_wbn_16.44_dec_0.316</t>
+    <t>043-03_0003_1_PK_km0869</t>
   </si>
 </sst>
 </file>
@@ -773,17 +774,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{11010186-4FF4-48E2-AD4E-93BC10A29908}"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <numFmt numFmtId="15" formatCode="0.00E+00"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -827,6 +825,9 @@
     <dxf>
       <numFmt numFmtId="15" formatCode="0.00E+00"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -841,25 +842,6 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4FDF574F-BB2D-4F45-983A-2F40030BA30E}" name="Tabel8" displayName="Tabel8" ref="A2:I4" headerRowCount="0" totalsRowShown="0">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{ED91B529-5CA2-45E4-9C35-FB2791BC9472}" name="Kolom1"/>
-    <tableColumn id="2" xr3:uid="{6451F148-AA59-4DB3-B134-BC4EA4C09A38}" name="Kolom2"/>
-    <tableColumn id="3" xr3:uid="{ED3D5EAC-E087-4743-8487-EF8C4C707E15}" name="Kolom3"/>
-    <tableColumn id="4" xr3:uid="{96F9E6E9-B6AE-4D96-B29D-4E3954133940}" name="Kolom4"/>
-    <tableColumn id="5" xr3:uid="{B8EB618A-EC9D-4075-A22E-E29A6DDD8687}" name="Kolom5"/>
-    <tableColumn id="6" xr3:uid="{14683B6E-A235-4D4A-AC6B-DF84FDD07CB0}" name="Kolom6"/>
-    <tableColumn id="7" xr3:uid="{7D04DB3F-88A2-4BEA-BA56-E8C526AE5450}" name="Kolom7"/>
-    <tableColumn id="8" xr3:uid="{E43E242C-E2DF-40D4-9306-2F6E194C37B4}" name="Kolom8"/>
-    <tableColumn id="9" xr3:uid="{0A91B959-6FA5-4373-8F21-907B723707BA}" name="Kolom9"/>
-    <tableColumn id="10" xr3:uid="{7C7DBA02-8FF7-4CB2-9A10-B2F42A3F041C}" name="Kolom10"/>
-    <tableColumn id="11" xr3:uid="{4D2C6EEB-BD36-4D62-BA43-E0E9049ADB77}" name="Kolom11"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D6DB1DEC-E085-4F6B-B7C4-D4E6DD7E1A8E}" name="Tabel9" displayName="Tabel9" ref="A2:M13" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="2" xr3:uid="{8990A576-5075-4246-8F9A-BA6C41A7A01C}" name="Kolom2"/>
@@ -880,7 +862,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9844274D-7B34-420F-9662-89C5C9A298BD}" name="Tabel10" displayName="Tabel10" ref="A2:N7" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="14">
     <tableColumn id="2" xr3:uid="{E80206AD-C5FD-4475-B5E4-08A08DA66E4A}" name="Kolom2"/>
@@ -895,7 +877,7 @@
     <tableColumn id="10" xr3:uid="{30E95029-7E84-4404-97EA-CC899B222DC3}" name="Kolom10"/>
     <tableColumn id="11" xr3:uid="{21D2E504-CBB5-45F7-9119-E1DA7B53C2D5}" name="Kolom11"/>
     <tableColumn id="12" xr3:uid="{FF7176FB-923E-4ECE-83AA-046E768AD06C}" name="Kolom12"/>
-    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="9" dataDxfId="0">
+    <tableColumn id="14" xr3:uid="{4E1A767E-8059-4EF5-B52B-A1637577AFDF}" name="Kolom14" headerRowDxfId="9" dataDxfId="8">
       <calculatedColumnFormula>300*10^(-6)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" xr3:uid="{E12738E9-E3E4-4A5D-81C1-E333D11489B2}" name="Kolom15"/>
@@ -904,7 +886,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{ECE0F829-0060-4D7E-94D4-430EA87FED82}" name="Tabel12" displayName="Tabel12" ref="A2:P69" headerRowCount="0" totalsRowShown="0">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P69">
     <sortCondition ref="D2:D69" customList="Input,Input,can also be calculated,Constant,Calculated"/>
@@ -919,9 +901,9 @@
     <tableColumn id="6" xr3:uid="{FA05A46A-DA45-4C6A-9D17-689A03B15BA8}" name="Kolom6"/>
     <tableColumn id="7" xr3:uid="{25871E16-DA07-4B31-A7EF-FBA1FEE488DB}" name="Kolom7"/>
     <tableColumn id="8" xr3:uid="{A229D98E-F2F0-4491-8C3C-1FB943EA5058}" name="Kolom8"/>
-    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="6" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{1FBE756B-5426-4436-B3C8-55410DF75FDB}" name="Kolom9" headerRowDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{B851468F-D94B-4F13-9CF8-13DADE13A2A8}" name="Kolom10" headerRowDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{41B8BB8E-854F-4E90-B76F-4066FB0CA9A2}" name="Kolom11" headerRowDxfId="5" dataDxfId="4"/>
     <tableColumn id="12" xr3:uid="{E7B2F49E-191F-4D24-8883-DCCF4F196399}" name="Kolom12"/>
     <tableColumn id="13" xr3:uid="{1DB6223F-5250-48AD-B68D-FD511FFC8150}" name="Kolom13"/>
     <tableColumn id="14" xr3:uid="{B2104B25-DEBD-4E44-A26A-46A71C2A832D}" name="Kolom14"/>
@@ -1354,9 +1336,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -4006,22 +3985,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>OR($D1="metadata", $D1="calculated")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F69">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>OR($E1="deterministic", ISBLANK($E1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:H69">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$D2&lt;&gt;"constant"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:J69">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AND($D2&lt;&gt;"variable",$D2&lt;&gt;"constant")</formula>
     </cfRule>
   </conditionalFormatting>
